--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 44 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 40 clubs short</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6317,8 +6317,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7145,8 +7145,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9073,8 +9073,8 @@
       <c r="T82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
+      <c r="U82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V82" s="9" t="n">
         <v>0</v>
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10200,8 +10200,8 @@
       <c r="P93" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q93" s="9" t="n">
-        <v>1</v>
+      <c r="Q93" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
@@ -12197,7 +12197,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12267,8 +12267,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12473,8 +12473,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12985,7 +12985,7 @@
         <v>1</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -16736,7 +16736,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16967,7 +16967,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -17099,7 +17099,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2054,7 +2058,11 @@
       <c r="AB13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2155,7 +2163,11 @@
       <c r="AB14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2256,7 +2268,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2458,7 +2474,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2559,7 +2579,11 @@
       <c r="AB18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2971,7 +2995,11 @@
       <c r="AB22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -6023,7 +6051,11 @@
       <c r="AB52" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6124,7 +6156,11 @@
       <c r="AB53" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC53" s="4" t="inlineStr"/>
+      <c r="AC53" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6225,7 +6261,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6738,7 +6778,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -8281,7 +8325,11 @@
       <c r="AB74" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8382,7 +8430,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8794,7 +8846,11 @@
       <c r="AB79" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -8895,7 +8951,11 @@
       <c r="AB80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9202,7 +9262,11 @@
       <c r="AB83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9408,7 +9472,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -10236,7 +10304,11 @@
       <c r="AB93" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC93" s="4" t="inlineStr"/>
+      <c r="AC93" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -11157,7 +11229,11 @@
       <c r="AB102" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11464,7 +11540,11 @@
       <c r="AB105" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11868,7 +11948,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -14445,7 +14529,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14546,7 +14634,11 @@
       <c r="AB135" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -15257,7 +15349,11 @@
       <c r="AB142" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC142" s="4" t="inlineStr"/>
+      <c r="AC142" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 40 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="X2" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="X3" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y3" s="9" t="n">
         <v>0</v>
@@ -1219,8 +1219,8 @@
       <c r="W5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="10" t="n">
-        <v>7</v>
+      <c r="X5" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1320,8 +1320,8 @@
       <c r="W6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="10" t="n">
-        <v>7</v>
+      <c r="X6" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8" s="9" t="n">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
         <v>4</v>
       </c>
       <c r="X10" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="X11" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>0</v>
@@ -2044,7 +2044,7 @@
         <v>2</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y13" s="9" t="n">
         <v>0</v>
@@ -2149,7 +2149,7 @@
         <v>3</v>
       </c>
       <c r="X14" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2358,8 +2358,8 @@
       <c r="W16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X16" s="10" t="n">
-        <v>7</v>
+      <c r="X16" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3196,8 +3196,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5044,8 +5044,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5836,8 +5836,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -7545,13 +7545,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8114,8 +8114,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8631,8 +8631,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9433,8 +9433,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P85" s="9" t="n">
-        <v>3</v>
+      <c r="P85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>0</v>
@@ -9613,13 +9613,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9924,13 +9924,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>4</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11430,8 +11430,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11475,13 +11475,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>6</v>
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11939,8 +11939,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -13329,13 +13329,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14415,8 +14415,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -16601,7 +16601,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16733,7 +16733,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16799,7 +16799,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -16931,7 +16931,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -16964,7 +16964,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -16997,7 +16997,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17129,7 +17129,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -17327,7 +17327,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 12 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1219,8 +1219,8 @@
       <c r="W5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="9" t="n">
-        <v>1</v>
+      <c r="X5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1320,8 +1320,8 @@
       <c r="W6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="9" t="n">
-        <v>0</v>
+      <c r="X6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2154,8 +2154,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>1</v>
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>5</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3604,8 +3604,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -4012,8 +4012,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4057,13 +4057,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
@@ -4113,8 +4113,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4323,8 +4323,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4735,8 +4735,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4825,8 +4825,8 @@
       <c r="T40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U40" s="9" t="n">
-        <v>0</v>
+      <c r="U40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V40" s="9" t="n">
         <v>1</v>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4945,8 +4945,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5539,8 +5539,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -8937,7 +8937,7 @@
         <v>6</v>
       </c>
       <c r="X80" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9337,8 +9337,8 @@
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S84" s="9" t="n">
-        <v>1</v>
+      <c r="S84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T84" s="10" t="n">
         <v>1</v>
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9613,13 +9613,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9669,8 +9669,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10812,8 +10812,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10913,8 +10913,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11719,8 +11719,8 @@
       <c r="S107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U107" s="9" t="n">
         <v>0</v>
@@ -11910,7 +11910,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -12382,7 +12382,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12422,8 +12422,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P114" s="9" t="n">
-        <v>3</v>
+      <c r="P114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>1</v>
@@ -12588,7 +12588,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12658,8 +12658,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12693,7 +12693,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12763,8 +12763,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13356,7 +13356,7 @@
         </is>
       </c>
       <c r="P123" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -13535,13 +13535,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -14337,15 +14337,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>3871</v>
+        <v>2390648</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Copenhagen Toastmasters Club</t>
+          <t>Copenhagen International Online Toastmasters</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14362,10 +14362,10 @@
         <v>17</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" s="8" t="inlineStr">
         <is>
@@ -14386,10 +14386,10 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q133" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -14400,17 +14400,17 @@
       <c r="T133" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U133" s="9" t="n">
-        <v>0</v>
+      <c r="U133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -14442,11 +14442,11 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>6786547</v>
+        <v>3871</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Frederiksberg Toastmasters</t>
+          <t>Copenhagen Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -14464,17 +14464,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="7" t="n">
@@ -14491,10 +14491,10 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q134" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -14502,14 +14502,14 @@
       <c r="S134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T134" s="9" t="n">
-        <v>0</v>
+      <c r="T134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -14527,11 +14527,11 @@
         <v>1</v>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC134" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -14547,15 +14547,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>6981382</v>
+        <v>6786547</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Speak To Lead Toastmasters</t>
+          <t>Frederiksberg Toastmasters</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14569,13 +14569,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -14596,10 +14596,10 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q135" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q135" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>0</v>
@@ -14614,13 +14614,13 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14652,15 +14652,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>2390648</v>
+        <v>6981382</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters CPH North</t>
+          <t>Speak To Lead Toastmasters</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14674,17 +14674,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M136" s="7" t="n">
@@ -14701,10 +14701,10 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q136" s="10" t="n">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="Q136" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -14712,36 +14712,36 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U136" s="10" t="n">
-        <v>1</v>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB136" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC136" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14936,8 +14936,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -15037,8 +15037,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -15068,7 +15068,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -15138,8 +15138,8 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15445,8 +15445,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -15581,7 +15581,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15651,8 +15651,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -16469,7 +16469,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16535,7 +16535,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -16634,7 +16634,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16700,7 +16700,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16733,7 +16733,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16766,7 +16766,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16997,7 +16997,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17030,7 +17030,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -17096,7 +17096,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -17195,7 +17195,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17327,7 +17327,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17360,7 +17360,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -17393,7 +17393,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 12 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 12 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -963,20 +963,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -984,7 +984,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1068,20 +1068,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1089,7 +1089,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1169,20 +1169,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1190,7 +1190,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1270,20 +1270,20 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1291,7 +1291,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1314,8 +1314,8 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1371,20 +1371,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
+        <v>-17</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="M7" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1392,7 +1392,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1472,20 +1472,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1493,7 +1493,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1516,8 +1516,8 @@
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>2</v>
+      <c r="V8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1577,20 +1577,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1598,7 +1598,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1682,20 +1682,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8</v>
+        <v>-7</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1703,16 +1703,16 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -1720,8 +1720,8 @@
       <c r="S10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>5</v>
@@ -1787,20 +1787,20 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1892,20 +1892,20 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1913,7 +1913,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1937,7 +1937,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1993,20 +1993,20 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -2014,7 +2014,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2040,8 +2040,8 @@
       <c r="V13" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>2</v>
+      <c r="W13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>5</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2098,20 +2098,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2119,7 +2119,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2140,13 +2140,13 @@
         <v>1</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V14" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W14" s="9" t="n">
-        <v>3</v>
+      <c r="W14" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>5</v>
@@ -2203,20 +2203,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="M15" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2224,7 +2224,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2321,7 +2321,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2329,7 +2329,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2409,20 +2409,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2430,7 +2430,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2441,11 +2441,11 @@
       <c r="Q17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R17" s="9" t="n">
-        <v>0</v>
+      <c r="R17" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="10" t="n">
         <v>1</v>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2514,20 +2514,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2619,20 +2619,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2640,7 +2640,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2720,20 +2720,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>146</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2741,7 +2741,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2768,7 +2768,7 @@
         <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>4</v>
@@ -2825,20 +2825,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2846,7 +2846,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2930,20 +2930,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2951,7 +2951,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3035,20 +3035,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -3056,7 +3056,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3140,20 +3140,20 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3161,7 +3161,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3184,8 +3184,8 @@
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>3</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3241,20 +3241,20 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3262,7 +3262,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3342,20 +3342,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3363,7 +3363,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3443,20 +3443,20 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3464,7 +3464,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3548,20 +3548,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3569,7 +3569,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3649,20 +3649,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M29" s="7" t="n">
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3670,7 +3670,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3750,20 +3750,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>-21</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3771,7 +3771,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3794,11 +3794,11 @@
       <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="9" t="n">
-        <v>1</v>
+      <c r="V30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" s="9" t="n">
         <v>2</v>
@@ -3863,12 +3863,12 @@
       <c r="K31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3876,7 +3876,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3964,12 +3964,12 @@
       <c r="K32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3977,7 +3977,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4057,20 +4057,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -4078,7 +4078,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4162,20 +4162,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M34" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -4183,7 +4183,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4267,20 +4267,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4288,7 +4288,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4312,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4372,20 +4372,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4393,7 +4393,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4416,11 +4416,11 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>1</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>5</v>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4473,20 +4473,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4494,7 +4494,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4517,8 +4517,8 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>1</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4578,20 +4578,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M38" s="7" t="n">
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4599,13 +4599,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>0</v>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4679,20 +4679,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4700,13 +4700,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4724,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4784,20 +4784,20 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4805,7 +4805,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4828,11 +4828,11 @@
       <c r="U40" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>1</v>
+      <c r="V40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" s="10" t="n">
         <v>6</v>
@@ -4889,20 +4889,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4910,7 +4910,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4988,20 +4988,20 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5032,8 +5032,8 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>1</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5087,20 +5087,20 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -5108,7 +5108,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5132,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5186,20 +5186,20 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -5207,7 +5207,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5285,20 +5285,20 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5306,7 +5306,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5392,12 +5392,12 @@
       <c r="K46" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L46" s="8" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5405,7 +5405,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5483,20 +5483,20 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M47" s="7" t="n">
+      <c r="M47" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -5504,7 +5504,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O47" s="8" t="inlineStr">
+      <c r="O47" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5582,20 +5582,20 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5603,7 +5603,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5627,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5681,20 +5681,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5702,7 +5702,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5780,20 +5780,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5801,7 +5801,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5816,7 +5816,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="9" t="n">
         <v>0</v>
@@ -5881,20 +5881,20 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5902,7 +5902,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5929,7 +5929,7 @@
         <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>5</v>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5986,20 +5986,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M52" s="7" t="n">
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -6007,7 +6007,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6030,11 +6030,11 @@
       <c r="U52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="9" t="n">
-        <v>3</v>
+      <c r="V52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>4</v>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6091,20 +6091,20 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M53" s="7" t="n">
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -6112,7 +6112,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6132,8 +6132,8 @@
       <c r="T53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
+      <c r="U53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V53" s="10" t="n">
         <v>4</v>
@@ -6196,20 +6196,20 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>14</v>
+        <v>-5</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -6217,7 +6217,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6244,7 +6244,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>7</v>
@@ -6309,12 +6309,12 @@
       <c r="K55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L55" s="8" t="inlineStr">
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M55" s="7" t="n">
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6322,7 +6322,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6346,7 +6346,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6402,20 +6402,20 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6423,7 +6423,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6503,20 +6503,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M57" s="7" t="n">
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6524,7 +6524,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6547,11 +6547,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>3</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7</v>
@@ -6608,20 +6608,20 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6629,7 +6629,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6713,20 +6713,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6734,7 +6734,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6758,7 +6758,7 @@
         <v>1</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6818,20 +6818,20 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6839,7 +6839,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6923,20 +6923,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6944,7 +6944,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6961,14 +6961,14 @@
       <c r="S61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7028,20 +7028,20 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>9</v>
+        <v>-5</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M62" s="7" t="n">
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -7049,7 +7049,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7146,7 +7146,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -7154,7 +7154,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7234,20 +7234,20 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -7255,7 +7255,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7335,20 +7335,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M65" s="7" t="n">
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -7356,7 +7356,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7440,20 +7440,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7461,7 +7461,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7545,38 +7545,38 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K67" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M67" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O67" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7650,20 +7650,20 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7671,7 +7671,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7695,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7751,20 +7751,20 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M69" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7772,7 +7772,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7864,12 +7864,12 @@
       <c r="K70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L70" s="8" t="inlineStr">
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M70" s="7" t="n">
+      <c r="M70" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7877,7 +7877,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7957,20 +7957,20 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L71" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7978,7 +7978,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8058,20 +8058,20 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -8079,7 +8079,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8159,20 +8159,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -8180,7 +8180,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8260,20 +8260,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -8281,7 +8281,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8290,7 +8290,7 @@
         <v>2</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8365,20 +8365,20 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M75" s="7" t="n">
+      <c r="M75" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -8386,7 +8386,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8412,8 +8412,8 @@
       <c r="V75" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W75" s="9" t="n">
-        <v>2</v>
+      <c r="W75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X75" s="10" t="n">
         <v>7</v>
@@ -8470,20 +8470,20 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M76" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8491,7 +8491,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8583,12 +8583,12 @@
       <c r="K77" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L77" s="8" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8596,7 +8596,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8619,8 +8619,8 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>1</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8676,20 +8676,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8697,7 +8697,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8721,7 +8721,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8781,20 +8781,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8802,7 +8802,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8814,7 +8814,7 @@
         <v>2</v>
       </c>
       <c r="R79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79" s="9" t="n">
         <v>1</v>
@@ -8829,7 +8829,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>5</v>
@@ -8886,20 +8886,20 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="M80" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8907,7 +8907,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8919,7 +8919,7 @@
         <v>2</v>
       </c>
       <c r="R80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" s="9" t="n">
         <v>1</v>
@@ -8934,7 +8934,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>7</v>
@@ -8991,20 +8991,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M81" s="7" t="n">
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -9012,7 +9012,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9092,20 +9092,20 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -9113,7 +9113,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9137,7 +9137,7 @@
         <v>1</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9197,20 +9197,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -9218,7 +9218,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9302,20 +9302,20 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M84" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -9323,7 +9323,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9407,20 +9407,20 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M85" s="7" t="n">
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -9428,25 +9428,25 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P85" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S85" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>6</v>
@@ -9512,20 +9512,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M86" s="7" t="n">
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9533,7 +9533,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9557,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9613,20 +9613,20 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M87" s="7" t="n">
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9634,7 +9634,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9714,20 +9714,20 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="M88" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9735,7 +9735,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9759,7 +9759,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9819,20 +9819,20 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M89" s="7" t="n">
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9840,7 +9840,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9937,7 +9937,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9945,13 +9945,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>1</v>
@@ -9972,7 +9972,7 @@
         <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>4</v>
@@ -10037,12 +10037,12 @@
       <c r="K91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L91" s="8" t="inlineStr">
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -10050,7 +10050,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10059,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -10134,20 +10134,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M92" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -10155,7 +10155,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10239,20 +10239,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10275,7 +10275,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" s="10" t="n">
         <v>1</v>
@@ -10287,7 +10287,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>5</v>
@@ -10330,7 +10330,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10344,37 +10344,37 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K94" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O94" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q94" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N94" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O94" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P94" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q94" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R94" s="9" t="n">
         <v>0</v>
@@ -10445,20 +10445,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M95" s="7" t="n">
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -10466,7 +10466,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10550,20 +10550,20 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="M96" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -10571,7 +10571,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10598,7 +10598,7 @@
         <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>4</v>
@@ -10663,12 +10663,12 @@
       <c r="K97" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L97" s="8" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10676,7 +10676,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10700,7 +10700,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10742,7 +10742,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10756,20 +10756,20 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M98" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M98" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10777,7 +10777,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10800,8 +10800,8 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>2</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10857,20 +10857,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M99" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10878,7 +10878,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10902,7 +10902,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10958,20 +10958,20 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M100" s="7" t="n">
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10979,7 +10979,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11002,8 +11002,8 @@
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>3</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11063,20 +11063,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
+        <v>-18</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="M101" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -11084,7 +11084,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11164,20 +11164,20 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -11185,7 +11185,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11269,20 +11269,20 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M103" s="7" t="n">
+        <v>-22</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M103" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -11290,7 +11290,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11374,20 +11374,20 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -11395,7 +11395,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11419,13 +11419,13 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X104" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -11461,7 +11461,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11475,20 +11475,20 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>7</v>
+        <v>-11</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M105" s="7" t="n">
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -11496,7 +11496,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11522,8 +11522,8 @@
       <c r="V105" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W105" s="9" t="n">
-        <v>3</v>
+      <c r="W105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>6</v>
@@ -11580,20 +11580,20 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M106" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -11601,7 +11601,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11625,7 +11625,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11681,20 +11681,20 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M107" s="7" t="n">
+      <c r="M107" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11702,7 +11702,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11782,20 +11782,20 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M108" s="7" t="n">
+      <c r="M108" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -11803,7 +11803,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O108" s="8" t="inlineStr">
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11830,7 +11830,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>4</v>
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11883,20 +11883,20 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M109" s="7" t="n">
+      <c r="M109" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -11904,13 +11904,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O109" s="8" t="inlineStr">
+      <c r="O109" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P109" s="9" t="n">
-        <v>3</v>
+      <c r="P109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11927,8 +11927,8 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="9" t="n">
-        <v>3</v>
+      <c r="V109" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11988,20 +11988,20 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M110" s="7" t="n">
+      <c r="M110" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -12009,7 +12009,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O110" s="8" t="inlineStr">
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12036,7 +12036,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="X110" s="9" t="n">
         <v>1</v>
@@ -12089,20 +12089,20 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M111" s="7" t="n">
+      <c r="M111" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -12110,7 +12110,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O111" s="8" t="inlineStr">
+      <c r="O111" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12137,7 +12137,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X111" s="10" t="n">
         <v>4</v>
@@ -12194,20 +12194,20 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L112" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M112" s="7" t="n">
+      <c r="M112" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -12215,7 +12215,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="O112" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12303,12 +12303,12 @@
       <c r="K113" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L113" s="8" t="inlineStr">
+      <c r="L113" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M113" s="7" t="n">
+      <c r="M113" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -12316,7 +12316,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O113" s="8" t="inlineStr">
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12340,7 +12340,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12396,20 +12396,20 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M114" s="7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M114" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -12417,7 +12417,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O114" s="8" t="inlineStr">
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12441,7 +12441,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12501,20 +12501,20 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M115" s="7" t="n">
+      <c r="M115" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -12522,7 +12522,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O115" s="8" t="inlineStr">
+      <c r="O115" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12602,20 +12602,20 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M116" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M116" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -12623,7 +12623,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O116" s="8" t="inlineStr">
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12707,20 +12707,20 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M117" s="7" t="n">
+      <c r="M117" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -12728,7 +12728,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O117" s="8" t="inlineStr">
+      <c r="O117" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12752,7 +12752,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12794,7 +12794,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12808,35 +12808,35 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K118" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M118" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O118" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P118" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M118" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N118" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O118" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P118" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="Q118" s="9" t="n">
         <v>0</v>
       </c>
@@ -12852,11 +12852,11 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>2</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>4</v>
@@ -12913,20 +12913,20 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M119" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M119" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -12934,7 +12934,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O119" s="8" t="inlineStr">
+      <c r="O119" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12958,7 +12958,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -13018,20 +13018,20 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M120" s="7" t="n">
+      <c r="M120" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -13039,7 +13039,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O120" s="8" t="inlineStr">
+      <c r="O120" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13066,7 +13066,7 @@
         <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>7</v>
@@ -13109,7 +13109,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13123,20 +13123,20 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M121" s="7" t="n">
+      <c r="M121" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -13144,7 +13144,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O121" s="8" t="inlineStr">
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13167,8 +13167,8 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>2</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -13228,20 +13228,20 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M122" s="7" t="n">
+      <c r="M122" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -13249,7 +13249,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O122" s="8" t="inlineStr">
+      <c r="O122" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13273,7 +13273,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13329,20 +13329,20 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M123" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M123" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -13350,7 +13350,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O123" s="8" t="inlineStr">
+      <c r="O123" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13359,13 +13359,13 @@
         <v>5</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123" s="9" t="n">
         <v>0</v>
@@ -13434,20 +13434,20 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M124" s="7" t="n">
+      <c r="M124" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -13455,7 +13455,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O124" s="8" t="inlineStr">
+      <c r="O124" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13479,7 +13479,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13521,7 +13521,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13535,20 +13535,20 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M125" s="7" t="n">
+      <c r="M125" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -13556,7 +13556,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O125" s="8" t="inlineStr">
+      <c r="O125" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13579,8 +13579,8 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>2</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -13640,20 +13640,20 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M126" s="7" t="n">
+      <c r="M126" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -13661,7 +13661,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O126" s="8" t="inlineStr">
+      <c r="O126" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13685,7 +13685,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13745,20 +13745,20 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M127" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M127" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -13766,7 +13766,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O127" s="8" t="inlineStr">
+      <c r="O127" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13790,7 +13790,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13846,20 +13846,20 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M128" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M128" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
@@ -13867,7 +13867,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O128" s="8" t="inlineStr">
+      <c r="O128" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13947,20 +13947,20 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M129" s="7" t="n">
+      <c r="M129" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
@@ -13968,7 +13968,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O129" s="8" t="inlineStr">
+      <c r="O129" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13992,7 +13992,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14048,20 +14048,20 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M130" s="7" t="n">
+      <c r="M130" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -14069,7 +14069,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O130" s="8" t="inlineStr">
+      <c r="O130" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14092,8 +14092,8 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>3</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14149,20 +14149,20 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M131" s="7" t="n">
+      <c r="M131" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -14170,7 +14170,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O131" s="8" t="inlineStr">
+      <c r="O131" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14193,8 +14193,8 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>3</v>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14240,7 +14240,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14254,20 +14254,20 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M132" s="7" t="n">
+      <c r="M132" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
@@ -14275,7 +14275,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O132" s="8" t="inlineStr">
+      <c r="O132" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14298,11 +14298,11 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>2</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>6</v>
@@ -14359,20 +14359,20 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
+        <v>-7</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M133" s="7" t="n">
+      <c r="M133" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
@@ -14380,7 +14380,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O133" s="8" t="inlineStr">
+      <c r="O133" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14464,20 +14464,20 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M134" s="7" t="n">
+      <c r="M134" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
@@ -14485,7 +14485,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O134" s="8" t="inlineStr">
+      <c r="O134" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14555,7 +14555,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14569,20 +14569,20 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M135" s="7" t="n">
+      <c r="M135" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -14590,7 +14590,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O135" s="8" t="inlineStr">
+      <c r="O135" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14613,11 +14613,11 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W135" s="9" t="n">
-        <v>0</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W135" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>5</v>
@@ -14674,20 +14674,20 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M136" s="7" t="n">
+      <c r="M136" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -14695,7 +14695,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O136" s="8" t="inlineStr">
+      <c r="O136" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14719,7 +14719,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14779,20 +14779,20 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M137" s="7" t="n">
+      <c r="M137" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
@@ -14800,7 +14800,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O137" s="8" t="inlineStr">
+      <c r="O137" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14880,20 +14880,20 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M138" s="7" t="n">
+      <c r="M138" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
@@ -14901,7 +14901,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O138" s="8" t="inlineStr">
+      <c r="O138" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14981,20 +14981,20 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M139" s="7" t="n">
+      <c r="M139" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
@@ -15002,7 +15002,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O139" s="8" t="inlineStr">
+      <c r="O139" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15026,7 +15026,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15082,20 +15082,20 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L140" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M140" s="7" t="n">
+      <c r="M140" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
@@ -15103,7 +15103,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O140" s="8" t="inlineStr">
+      <c r="O140" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15130,7 +15130,7 @@
         <v>4</v>
       </c>
       <c r="W140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X140" s="9" t="n">
         <v>3</v>
@@ -15183,20 +15183,20 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="8" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M141" s="7" t="n">
+      <c r="M141" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N141" s="4" t="inlineStr">
@@ -15204,7 +15204,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O141" s="8" t="inlineStr">
+      <c r="O141" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15284,20 +15284,20 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M142" s="7" t="n">
+      <c r="M142" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
@@ -15305,7 +15305,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O142" s="8" t="inlineStr">
+      <c r="O142" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15332,7 +15332,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X142" s="10" t="n">
         <v>6</v>
@@ -15389,20 +15389,20 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M143" s="7" t="n">
+      <c r="M143" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -15410,7 +15410,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O143" s="8" t="inlineStr">
+      <c r="O143" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15434,7 +15434,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15480,7 +15480,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15494,20 +15494,20 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M144" s="7" t="n">
+      <c r="M144" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
@@ -15515,13 +15515,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O144" s="8" t="inlineStr">
+      <c r="O144" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P144" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -15529,8 +15529,8 @@
       <c r="R144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S144" s="9" t="n">
-        <v>1</v>
+      <c r="S144" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T144" s="10" t="n">
         <v>1</v>
@@ -15595,20 +15595,20 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M145" s="7" t="n">
+      <c r="M145" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
@@ -15616,7 +15616,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O145" s="8" t="inlineStr">
+      <c r="O145" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15640,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15696,20 +15696,20 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M146" s="7" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M146" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
@@ -15717,7 +15717,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O146" s="8" t="inlineStr">
+      <c r="O146" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15801,20 +15801,20 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M147" s="7" t="n">
+      <c r="M147" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
@@ -15822,7 +15822,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O147" s="8" t="inlineStr">
+      <c r="O147" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15846,7 +15846,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15902,20 +15902,20 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M148" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M148" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N148" s="4" t="inlineStr">
@@ -15923,7 +15923,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O148" s="8" t="inlineStr">
+      <c r="O148" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16007,20 +16007,20 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M149" s="7" t="n">
+      <c r="M149" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -16028,7 +16028,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O149" s="8" t="inlineStr">
+      <c r="O149" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16052,7 +16052,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -16108,20 +16108,20 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M150" s="7" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M150" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N150" s="4" t="inlineStr">
@@ -16129,7 +16129,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O150" s="8" t="inlineStr">
+      <c r="O150" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16209,20 +16209,20 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M151" s="7" t="n">
+      <c r="M151" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -16230,7 +16230,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O151" s="8" t="inlineStr">
+      <c r="O151" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16250,11 +16250,11 @@
       <c r="T151" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V151" s="9" t="n">
-        <v>2</v>
+      <c r="U151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V151" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -16314,20 +16314,20 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M152" s="7" t="n">
+      <c r="M152" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -16335,7 +16335,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O152" s="8" t="inlineStr">
+      <c r="O152" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16469,7 +16469,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16484,7 +16484,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -16502,13 +16502,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -16517,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -16535,13 +16535,13 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -16601,7 +16601,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -16634,7 +16634,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16682,7 +16682,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -16700,13 +16700,13 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -16715,7 +16715,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -16733,7 +16733,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16748,7 +16748,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -16799,7 +16799,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -16832,7 +16832,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16865,7 +16865,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16898,7 +16898,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16913,7 +16913,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -16931,7 +16931,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -16946,7 +16946,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -16964,7 +16964,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -16979,7 +16979,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -16997,13 +16997,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -17012,7 +17012,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -17063,7 +17063,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -17078,7 +17078,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -17096,7 +17096,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17111,7 +17111,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -17129,7 +17129,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17144,7 +17144,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -17162,7 +17162,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -17210,7 +17210,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -17228,7 +17228,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -17243,7 +17243,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -17261,7 +17261,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -17294,7 +17294,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17309,7 +17309,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -17327,7 +17327,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17393,13 +17393,13 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -17408,7 +17408,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -17426,7 +17426,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17441,7 +17441,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 12 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 12 clubs short</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1615,8 +1615,8 @@
       <c r="S9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="9" t="n">
-        <v>0</v>
+      <c r="T9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U9" s="9" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2133,8 +2133,8 @@
       <c r="R14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="9" t="n">
-        <v>1</v>
+      <c r="S14" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T14" s="10" t="n">
         <v>1</v>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="P18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2720,13 +2720,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>146</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2767,8 +2767,8 @@
       <c r="V20" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W20" s="9" t="n">
-        <v>2</v>
+      <c r="W20" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>4</v>
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -3140,17 +3140,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M24" s="8" t="n">
@@ -3188,7 +3188,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>6</v>
@@ -3342,13 +3342,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3443,13 +3443,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-21</v>
+        <v>-18</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>5</v>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>5</v>
@@ -4988,17 +4988,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="9" t="n">
         <v>0</v>
@@ -5186,13 +5186,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5236,8 +5236,8 @@
       <c r="W44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X44" s="9" t="n">
-        <v>2</v>
+      <c r="X44" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5527,11 +5527,11 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>1</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>4</v>
@@ -7064,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7545,13 +7545,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7589,8 +7589,8 @@
       <c r="U67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="9" t="n">
-        <v>3</v>
+      <c r="V67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7751,17 +7751,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7957,13 +7957,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8260,13 +8260,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -9092,13 +9092,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -9197,13 +9197,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10265,8 +10265,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P93" s="9" t="n">
-        <v>3</v>
+      <c r="P93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q93" s="10" t="n">
         <v>2</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10597,8 +10597,8 @@
       <c r="V96" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W96" s="9" t="n">
-        <v>2</v>
+      <c r="W96" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>4</v>
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q100" s="10" t="n">
         <v>2</v>
@@ -11063,13 +11063,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-18</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11475,13 +11475,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11523,7 +11523,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>6</v>
@@ -11913,7 +11913,7 @@
         <v>4</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
@@ -11988,13 +11988,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X110" s="9" t="n">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12382,7 +12382,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12396,13 +12396,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12440,8 +12440,8 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>2</v>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12913,13 +12913,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -13329,13 +13329,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -14254,13 +14254,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>6</v>
@@ -14359,13 +14359,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>2</v>
       </c>
       <c r="R135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S135" s="9" t="n">
         <v>0</v>
@@ -15320,7 +15320,7 @@
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T142" s="10" t="n">
         <v>1</v>
@@ -15494,13 +15494,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15696,13 +15696,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -16209,13 +16209,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>4</v>
       </c>
       <c r="W151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>6</v>
@@ -16362,7 +16362,7 @@
         <v>4</v>
       </c>
       <c r="W152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X152" s="10" t="n">
         <v>5</v>
@@ -16502,7 +16502,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -16535,7 +16535,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -16568,7 +16568,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -16748,7 +16748,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -16766,7 +16766,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16898,7 +16898,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16913,7 +16913,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -17063,13 +17063,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -17096,13 +17096,13 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -17195,7 +17195,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/95/inyear.xlsx
+++ b/docs/d/95/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 3 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 3 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 12 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 12 clubs short</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1577,17 +1577,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1621,8 +1621,8 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>3</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2444,8 +2444,8 @@
       <c r="R17" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S17" s="9" t="n">
-        <v>1</v>
+      <c r="S17" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T17" s="10" t="n">
         <v>1</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>53</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X30" s="9" t="n">
         <v>2</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>0</v>
@@ -5681,13 +5681,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="P53" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q53" s="10" t="n">
         <v>2</v>
@@ -6539,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="10" t="n">
         <v>1</v>
@@ -7028,13 +7028,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>1</v>
@@ -7076,7 +7076,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>4</v>
@@ -7133,13 +7133,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7234,13 +7234,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
         <v>2</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -8365,13 +8365,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9407,13 +9407,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="P85" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q85" s="9" t="n">
         <v>1</v>
@@ -9454,8 +9454,8 @@
       <c r="V85" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W85" s="9" t="n">
-        <v>1</v>
+      <c r="W85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>6</v>
@@ -10272,7 +10272,7 @@
         <v>2</v>
       </c>
       <c r="R93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93" s="9" t="n">
         <v>1</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11418,8 +11418,8 @@
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="9" t="n">
-        <v>3</v>
+      <c r="V104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11461,7 +11461,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11501,8 +11501,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P105" s="9" t="n">
-        <v>3</v>
+      <c r="P105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11681,13 +11681,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11725,8 +11725,8 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="9" t="n">
-        <v>3</v>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11768,7 +11768,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11782,13 +11782,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11829,8 +11829,8 @@
       <c r="V108" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>1</v>
+      <c r="W108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>4</v>
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11918,8 +11918,8 @@
       <c r="R109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S109" s="9" t="n">
-        <v>1</v>
+      <c r="S109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -13153,7 +13153,7 @@
         <v>2</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13228,13 +13228,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13521,7 +13521,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13567,8 +13567,8 @@
       <c r="Q125" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R125" s="9" t="n">
-        <v>1</v>
+      <c r="R125" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S125" s="9" t="n">
         <v>0</v>
@@ -13670,7 +13670,7 @@
         <v>0</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -14555,7 +14555,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14595,17 +14595,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P135" s="9" t="n">
-        <v>3</v>
+      <c r="P135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q135" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S135" s="9" t="n">
-        <v>0</v>
+      <c r="R135" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S135" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T135" s="9" t="n">
         <v>0</v>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14674,13 +14674,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -14718,8 +14718,8 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>3</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14981,13 +14981,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15480,7 +15480,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15523,8 +15523,8 @@
       <c r="P144" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Q144" s="9" t="n">
-        <v>0</v>
+      <c r="Q144" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R144" s="9" t="n">
         <v>0</v>
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16209,13 +16209,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
@@ -16256,8 +16256,8 @@
       <c r="V151" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W151" s="9" t="n">
-        <v>1</v>
+      <c r="W151" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X151" s="10" t="n">
         <v>6</v>
@@ -16502,7 +16502,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -16517,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -16535,7 +16535,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -16997,7 +16997,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -17129,13 +17129,13 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -17261,7 +17261,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17327,13 +17327,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -17393,7 +17393,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -17426,13 +17426,13 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
